--- a/CHARMS COLGANTES DISNEY.xlsx
+++ b/CHARMS COLGANTES DISNEY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802CAABD-5A7C-49E8-BFB7-0564CD18F160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBD367D-23EE-4138-BC78-CFD7F76C1933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44B837E0-01FB-47FB-9746-0A32C4320ACA}"/>
   </bookViews>
@@ -12658,11 +12658,11 @@
         <f t="shared" ref="G4:G67" si="6">F4+10</f>
         <v>65</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10">
         <v>1</v>
       </c>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
@@ -12687,11 +12687,11 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10">
         <v>1</v>
       </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
@@ -12824,11 +12824,11 @@
         <f t="shared" si="6"/>
         <v>70</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
         <v>1</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
@@ -12961,11 +12961,11 @@
         <f t="shared" si="6"/>
         <v>70</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10">
         <v>1</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
     </row>
     <row r="16" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
@@ -13044,9 +13044,7 @@
         <f t="shared" si="6"/>
         <v>70</v>
       </c>
-      <c r="I18" s="10">
-        <v>1</v>
-      </c>
+      <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
     </row>
@@ -13586,11 +13584,11 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10">
         <v>1</v>
       </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
@@ -13723,11 +13721,11 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10">
         <v>1</v>
       </c>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
     </row>
     <row r="44" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">

--- a/CHARMS COLGANTES DISNEY.xlsx
+++ b/CHARMS COLGANTES DISNEY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FC1EF4-7D6D-4925-9CC7-242A3897357F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BE15C8-283E-431F-B9EC-B36990C02E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44B837E0-01FB-47FB-9746-0A32C4320ACA}"/>
   </bookViews>
@@ -12974,21 +12974,22 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="8">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="D8" s="9">
         <f t="shared" ref="D8" si="12">(C8*8)+3</f>
-        <v>3</v>
+        <v>33.480000000000004</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" ref="E8" si="13">D8*2</f>
-        <v>6</v>
+        <v>66.960000000000008</v>
       </c>
       <c r="F8" s="9">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G8" s="9">
-        <v>70</v>
+        <f t="shared" ref="G8:G72" si="14">F8+10</f>
+        <v>80</v>
       </c>
       <c r="I8" s="10"/>
       <c r="J8" s="10"/>
@@ -13003,18 +13004,18 @@
         <v>2.89</v>
       </c>
       <c r="D9" s="9">
-        <f t="shared" ref="D9:D72" si="14">(C9*8)+3</f>
+        <f t="shared" ref="D9:D72" si="15">(C9*8)+3</f>
         <v>26.12</v>
       </c>
       <c r="E9" s="9">
-        <f t="shared" ref="E9:E72" si="15">D9*2</f>
+        <f t="shared" ref="E9:E72" si="16">D9*2</f>
         <v>52.24</v>
       </c>
       <c r="F9" s="9">
         <v>55</v>
       </c>
       <c r="G9" s="9">
-        <f t="shared" ref="G9:G72" si="16">F9+10</f>
+        <f t="shared" si="14"/>
         <v>65</v>
       </c>
       <c r="I9" s="10"/>
@@ -13032,18 +13033,18 @@
         <v>3.42</v>
       </c>
       <c r="D10" s="9">
+        <f t="shared" si="15"/>
+        <v>30.36</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="16"/>
+        <v>60.72</v>
+      </c>
+      <c r="F10" s="9">
+        <v>65</v>
+      </c>
+      <c r="G10" s="9">
         <f t="shared" si="14"/>
-        <v>30.36</v>
-      </c>
-      <c r="E10" s="9">
-        <f t="shared" si="15"/>
-        <v>60.72</v>
-      </c>
-      <c r="F10" s="9">
-        <v>65</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="16"/>
         <v>75</v>
       </c>
       <c r="I10" s="10"/>
@@ -13061,18 +13062,18 @@
         <v>0</v>
       </c>
       <c r="D11" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F11" s="9">
+        <v>55</v>
+      </c>
+      <c r="G11" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E11" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F11" s="9">
-        <v>55</v>
-      </c>
-      <c r="G11" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I11" s="10"/>
@@ -13088,18 +13089,18 @@
         <v>0</v>
       </c>
       <c r="D12" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F12" s="9">
+        <v>55</v>
+      </c>
+      <c r="G12" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E12" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F12" s="9">
-        <v>55</v>
-      </c>
-      <c r="G12" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I12" s="10"/>
@@ -13115,18 +13116,18 @@
         <v>0</v>
       </c>
       <c r="D13" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F13" s="9">
+        <v>55</v>
+      </c>
+      <c r="G13" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F13" s="9">
-        <v>55</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I13" s="10"/>
@@ -13142,18 +13143,18 @@
         <v>0</v>
       </c>
       <c r="D14" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E14" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F14" s="9">
+        <v>55</v>
+      </c>
+      <c r="G14" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E14" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F14" s="9">
-        <v>55</v>
-      </c>
-      <c r="G14" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I14" s="10"/>
@@ -13169,18 +13170,18 @@
         <v>3.16</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>28.28</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>56.56</v>
       </c>
       <c r="F15" s="9">
         <v>60</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="I15" s="10"/>
@@ -13198,18 +13199,18 @@
         <v>0</v>
       </c>
       <c r="D16" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F16" s="9">
+        <v>55</v>
+      </c>
+      <c r="G16" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F16" s="9">
-        <v>55</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I16" s="10"/>
@@ -13225,18 +13226,18 @@
         <v>0</v>
       </c>
       <c r="D17" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E17" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F17" s="9">
+        <v>55</v>
+      </c>
+      <c r="G17" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E17" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F17" s="9">
-        <v>55</v>
-      </c>
-      <c r="G17" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I17" s="10"/>
@@ -13252,18 +13253,18 @@
         <v>0</v>
       </c>
       <c r="D18" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F18" s="9">
+        <v>55</v>
+      </c>
+      <c r="G18" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E18" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F18" s="9">
-        <v>55</v>
-      </c>
-      <c r="G18" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I18" s="10"/>
@@ -13279,18 +13280,18 @@
         <v>0</v>
       </c>
       <c r="D19" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E19" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F19" s="9">
+        <v>55</v>
+      </c>
+      <c r="G19" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E19" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F19" s="9">
-        <v>55</v>
-      </c>
-      <c r="G19" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I19" s="10"/>
@@ -13306,18 +13307,18 @@
         <v>3.16</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>28.28</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>56.56</v>
       </c>
       <c r="F20" s="9">
         <v>60</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="I20" s="10"/>
@@ -13335,18 +13336,18 @@
         <v>0</v>
       </c>
       <c r="D21" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E21" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F21" s="9">
+        <v>55</v>
+      </c>
+      <c r="G21" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E21" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F21" s="9">
-        <v>55</v>
-      </c>
-      <c r="G21" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I21" s="10"/>
@@ -13362,18 +13363,18 @@
         <v>0</v>
       </c>
       <c r="D22" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E22" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F22" s="9">
+        <v>55</v>
+      </c>
+      <c r="G22" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E22" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F22" s="9">
-        <v>55</v>
-      </c>
-      <c r="G22" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I22" s="10"/>
@@ -13389,18 +13390,18 @@
         <v>3.16</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>28.28</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>56.56</v>
       </c>
       <c r="F23" s="9">
         <v>60</v>
       </c>
       <c r="G23" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="I23" s="10"/>
@@ -13416,18 +13417,18 @@
         <v>0</v>
       </c>
       <c r="D24" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E24" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F24" s="9">
+        <v>55</v>
+      </c>
+      <c r="G24" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E24" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F24" s="9">
-        <v>55</v>
-      </c>
-      <c r="G24" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I24" s="10"/>
@@ -13443,18 +13444,18 @@
         <v>0</v>
       </c>
       <c r="D25" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E25" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F25" s="9">
+        <v>55</v>
+      </c>
+      <c r="G25" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E25" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F25" s="9">
-        <v>55</v>
-      </c>
-      <c r="G25" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I25" s="10"/>
@@ -13470,18 +13471,18 @@
         <v>0</v>
       </c>
       <c r="D26" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F26" s="9">
+        <v>55</v>
+      </c>
+      <c r="G26" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E26" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F26" s="9">
-        <v>55</v>
-      </c>
-      <c r="G26" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I26" s="10"/>
@@ -13497,18 +13498,18 @@
         <v>0</v>
       </c>
       <c r="D27" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F27" s="9">
+        <v>55</v>
+      </c>
+      <c r="G27" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E27" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F27" s="9">
-        <v>55</v>
-      </c>
-      <c r="G27" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I27" s="10"/>
@@ -13524,18 +13525,18 @@
         <v>0</v>
       </c>
       <c r="D28" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E28" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F28" s="9">
+        <v>55</v>
+      </c>
+      <c r="G28" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E28" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F28" s="9">
-        <v>55</v>
-      </c>
-      <c r="G28" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I28" s="10"/>
@@ -13551,18 +13552,18 @@
         <v>0</v>
       </c>
       <c r="D29" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E29" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F29" s="9">
+        <v>55</v>
+      </c>
+      <c r="G29" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E29" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F29" s="9">
-        <v>55</v>
-      </c>
-      <c r="G29" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I29" s="10"/>
@@ -13578,18 +13579,18 @@
         <v>0</v>
       </c>
       <c r="D30" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E30" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F30" s="9">
+        <v>55</v>
+      </c>
+      <c r="G30" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E30" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F30" s="9">
-        <v>55</v>
-      </c>
-      <c r="G30" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I30" s="10"/>
@@ -13605,18 +13606,18 @@
         <v>0</v>
       </c>
       <c r="D31" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E31" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F31" s="9">
+        <v>55</v>
+      </c>
+      <c r="G31" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E31" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F31" s="9">
-        <v>55</v>
-      </c>
-      <c r="G31" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I31" s="10"/>
@@ -13632,18 +13633,18 @@
         <v>3.29</v>
       </c>
       <c r="D32" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>29.32</v>
       </c>
       <c r="E32" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>58.64</v>
       </c>
       <c r="F32" s="9">
         <v>60</v>
       </c>
       <c r="G32" s="9">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="I32" s="10"/>
@@ -13659,18 +13660,18 @@
         <v>0</v>
       </c>
       <c r="D33" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E33" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F33" s="9">
+        <v>55</v>
+      </c>
+      <c r="G33" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E33" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F33" s="9">
-        <v>55</v>
-      </c>
-      <c r="G33" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I33" s="10"/>
@@ -13686,18 +13687,18 @@
         <v>0</v>
       </c>
       <c r="D34" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E34" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F34" s="9">
+        <v>55</v>
+      </c>
+      <c r="G34" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E34" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F34" s="9">
-        <v>55</v>
-      </c>
-      <c r="G34" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I34" s="10"/>
@@ -13713,18 +13714,18 @@
         <v>0</v>
       </c>
       <c r="D35" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E35" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F35" s="9">
+        <v>55</v>
+      </c>
+      <c r="G35" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E35" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F35" s="9">
-        <v>55</v>
-      </c>
-      <c r="G35" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I35" s="10"/>
@@ -13740,18 +13741,18 @@
         <v>2.89</v>
       </c>
       <c r="D36" s="9">
+        <f t="shared" si="15"/>
+        <v>26.12</v>
+      </c>
+      <c r="E36" s="9">
+        <f t="shared" si="16"/>
+        <v>52.24</v>
+      </c>
+      <c r="F36" s="9">
+        <v>55</v>
+      </c>
+      <c r="G36" s="9">
         <f t="shared" si="14"/>
-        <v>26.12</v>
-      </c>
-      <c r="E36" s="9">
-        <f t="shared" si="15"/>
-        <v>52.24</v>
-      </c>
-      <c r="F36" s="9">
-        <v>55</v>
-      </c>
-      <c r="G36" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I36" s="10"/>
@@ -13767,18 +13768,18 @@
         <v>0</v>
       </c>
       <c r="D37" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E37" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F37" s="9">
+        <v>55</v>
+      </c>
+      <c r="G37" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E37" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F37" s="9">
-        <v>55</v>
-      </c>
-      <c r="G37" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I37" s="10"/>
@@ -13794,18 +13795,18 @@
         <v>0</v>
       </c>
       <c r="D38" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E38" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F38" s="9">
+        <v>55</v>
+      </c>
+      <c r="G38" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E38" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F38" s="9">
-        <v>55</v>
-      </c>
-      <c r="G38" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I38" s="10"/>
@@ -13821,18 +13822,18 @@
         <v>2.89</v>
       </c>
       <c r="D39" s="9">
+        <f t="shared" si="15"/>
+        <v>26.12</v>
+      </c>
+      <c r="E39" s="9">
+        <f t="shared" si="16"/>
+        <v>52.24</v>
+      </c>
+      <c r="F39" s="9">
+        <v>55</v>
+      </c>
+      <c r="G39" s="9">
         <f t="shared" si="14"/>
-        <v>26.12</v>
-      </c>
-      <c r="E39" s="9">
-        <f t="shared" si="15"/>
-        <v>52.24</v>
-      </c>
-      <c r="F39" s="9">
-        <v>55</v>
-      </c>
-      <c r="G39" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I39" s="10"/>
@@ -13848,18 +13849,18 @@
         <v>0</v>
       </c>
       <c r="D40" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E40" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F40" s="9">
+        <v>55</v>
+      </c>
+      <c r="G40" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E40" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F40" s="9">
-        <v>55</v>
-      </c>
-      <c r="G40" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I40" s="10"/>
@@ -13875,18 +13876,18 @@
         <v>0</v>
       </c>
       <c r="D41" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E41" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F41" s="9">
+        <v>55</v>
+      </c>
+      <c r="G41" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E41" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F41" s="9">
-        <v>55</v>
-      </c>
-      <c r="G41" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I41" s="10"/>
@@ -13902,18 +13903,18 @@
         <v>0</v>
       </c>
       <c r="D42" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E42" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F42" s="9">
+        <v>55</v>
+      </c>
+      <c r="G42" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E42" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F42" s="9">
-        <v>55</v>
-      </c>
-      <c r="G42" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I42" s="10"/>
@@ -13929,18 +13930,18 @@
         <v>3.42</v>
       </c>
       <c r="D43" s="9">
+        <f t="shared" si="15"/>
+        <v>30.36</v>
+      </c>
+      <c r="E43" s="9">
+        <f t="shared" si="16"/>
+        <v>60.72</v>
+      </c>
+      <c r="F43" s="9">
+        <v>65</v>
+      </c>
+      <c r="G43" s="9">
         <f t="shared" si="14"/>
-        <v>30.36</v>
-      </c>
-      <c r="E43" s="9">
-        <f t="shared" si="15"/>
-        <v>60.72</v>
-      </c>
-      <c r="F43" s="9">
-        <v>65</v>
-      </c>
-      <c r="G43" s="9">
-        <f t="shared" si="16"/>
         <v>75</v>
       </c>
       <c r="I43" s="10"/>
@@ -13958,18 +13959,18 @@
         <v>0</v>
       </c>
       <c r="D44" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E44" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F44" s="9">
+        <v>55</v>
+      </c>
+      <c r="G44" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E44" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F44" s="9">
-        <v>55</v>
-      </c>
-      <c r="G44" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I44" s="10"/>
@@ -13985,18 +13986,18 @@
         <v>0</v>
       </c>
       <c r="D45" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E45" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F45" s="9">
+        <v>55</v>
+      </c>
+      <c r="G45" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E45" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F45" s="9">
-        <v>55</v>
-      </c>
-      <c r="G45" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I45" s="10"/>
@@ -14012,18 +14013,18 @@
         <v>0</v>
       </c>
       <c r="D46" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E46" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F46" s="9">
+        <v>55</v>
+      </c>
+      <c r="G46" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E46" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F46" s="9">
-        <v>55</v>
-      </c>
-      <c r="G46" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I46" s="10"/>
@@ -14039,18 +14040,18 @@
         <v>0</v>
       </c>
       <c r="D47" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E47" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F47" s="9">
+        <v>55</v>
+      </c>
+      <c r="G47" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E47" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F47" s="9">
-        <v>55</v>
-      </c>
-      <c r="G47" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I47" s="10"/>
@@ -14066,18 +14067,18 @@
         <v>3.55</v>
       </c>
       <c r="D48" s="9">
+        <f t="shared" si="15"/>
+        <v>31.4</v>
+      </c>
+      <c r="E48" s="9">
+        <f t="shared" si="16"/>
+        <v>62.8</v>
+      </c>
+      <c r="F48" s="9">
+        <v>65</v>
+      </c>
+      <c r="G48" s="9">
         <f t="shared" si="14"/>
-        <v>31.4</v>
-      </c>
-      <c r="E48" s="9">
-        <f t="shared" si="15"/>
-        <v>62.8</v>
-      </c>
-      <c r="F48" s="9">
-        <v>65</v>
-      </c>
-      <c r="G48" s="9">
-        <f t="shared" si="16"/>
         <v>75</v>
       </c>
       <c r="I48" s="10"/>
@@ -14095,18 +14096,18 @@
         <v>0</v>
       </c>
       <c r="D49" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E49" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F49" s="9">
+        <v>55</v>
+      </c>
+      <c r="G49" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E49" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F49" s="9">
-        <v>55</v>
-      </c>
-      <c r="G49" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I49" s="10"/>
@@ -14122,18 +14123,18 @@
         <v>0</v>
       </c>
       <c r="D50" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E50" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F50" s="9">
+        <v>55</v>
+      </c>
+      <c r="G50" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E50" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F50" s="9">
-        <v>55</v>
-      </c>
-      <c r="G50" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I50" s="10"/>
@@ -14146,22 +14147,22 @@
       </c>
       <c r="B51" s="11"/>
       <c r="C51" s="8">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="D51" s="9">
+        <f t="shared" si="15"/>
+        <v>30.36</v>
+      </c>
+      <c r="E51" s="9">
+        <f t="shared" si="16"/>
+        <v>60.72</v>
+      </c>
+      <c r="F51" s="9">
+        <v>65</v>
+      </c>
+      <c r="G51" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E51" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F51" s="9">
-        <v>55</v>
-      </c>
-      <c r="G51" s="9">
-        <f t="shared" si="16"/>
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I51" s="10"/>
       <c r="J51" s="10"/>
@@ -14176,18 +14177,18 @@
         <v>0</v>
       </c>
       <c r="D52" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E52" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F52" s="9">
+        <v>55</v>
+      </c>
+      <c r="G52" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E52" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F52" s="9">
-        <v>55</v>
-      </c>
-      <c r="G52" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I52" s="10"/>
@@ -14203,18 +14204,18 @@
         <v>0</v>
       </c>
       <c r="D53" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E53" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F53" s="9">
+        <v>55</v>
+      </c>
+      <c r="G53" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E53" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F53" s="9">
-        <v>55</v>
-      </c>
-      <c r="G53" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I53" s="10"/>
@@ -14230,18 +14231,18 @@
         <v>0</v>
       </c>
       <c r="D54" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E54" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F54" s="9">
+        <v>55</v>
+      </c>
+      <c r="G54" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E54" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F54" s="9">
-        <v>55</v>
-      </c>
-      <c r="G54" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I54" s="10"/>
@@ -14257,18 +14258,18 @@
         <v>0</v>
       </c>
       <c r="D55" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E55" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F55" s="9">
+        <v>55</v>
+      </c>
+      <c r="G55" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E55" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F55" s="9">
-        <v>55</v>
-      </c>
-      <c r="G55" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I55" s="10"/>
@@ -14284,18 +14285,18 @@
         <v>0</v>
       </c>
       <c r="D56" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E56" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F56" s="9">
+        <v>55</v>
+      </c>
+      <c r="G56" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E56" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F56" s="9">
-        <v>55</v>
-      </c>
-      <c r="G56" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I56" s="10"/>
@@ -14311,18 +14312,18 @@
         <v>0</v>
       </c>
       <c r="D57" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E57" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F57" s="9">
+        <v>55</v>
+      </c>
+      <c r="G57" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E57" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F57" s="9">
-        <v>55</v>
-      </c>
-      <c r="G57" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I57" s="10"/>
@@ -14338,18 +14339,18 @@
         <v>0</v>
       </c>
       <c r="D58" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E58" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F58" s="9">
+        <v>55</v>
+      </c>
+      <c r="G58" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E58" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F58" s="9">
-        <v>55</v>
-      </c>
-      <c r="G58" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I58" s="10"/>
@@ -14365,18 +14366,18 @@
         <v>0</v>
       </c>
       <c r="D59" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E59" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F59" s="9">
+        <v>55</v>
+      </c>
+      <c r="G59" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E59" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F59" s="9">
-        <v>55</v>
-      </c>
-      <c r="G59" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I59" s="10"/>
@@ -14392,18 +14393,18 @@
         <v>0</v>
       </c>
       <c r="D60" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E60" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F60" s="9">
+        <v>55</v>
+      </c>
+      <c r="G60" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E60" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F60" s="9">
-        <v>55</v>
-      </c>
-      <c r="G60" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I60" s="10"/>
@@ -14416,22 +14417,22 @@
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="8">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="D61" s="9">
+        <f t="shared" si="15"/>
+        <v>28.28</v>
+      </c>
+      <c r="E61" s="9">
+        <f t="shared" si="16"/>
+        <v>56.56</v>
+      </c>
+      <c r="F61" s="9">
+        <v>60</v>
+      </c>
+      <c r="G61" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E61" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F61" s="9">
-        <v>55</v>
-      </c>
-      <c r="G61" s="9">
-        <f t="shared" si="16"/>
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="10"/>
@@ -14446,18 +14447,18 @@
         <v>0</v>
       </c>
       <c r="D62" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E62" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F62" s="9">
+        <v>55</v>
+      </c>
+      <c r="G62" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E62" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F62" s="9">
-        <v>55</v>
-      </c>
-      <c r="G62" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I62" s="10"/>
@@ -14473,18 +14474,18 @@
         <v>0</v>
       </c>
       <c r="D63" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E63" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F63" s="9">
+        <v>55</v>
+      </c>
+      <c r="G63" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E63" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F63" s="9">
-        <v>55</v>
-      </c>
-      <c r="G63" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I63" s="10"/>
@@ -14500,18 +14501,18 @@
         <v>0</v>
       </c>
       <c r="D64" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E64" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F64" s="9">
+        <v>55</v>
+      </c>
+      <c r="G64" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E64" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F64" s="9">
-        <v>55</v>
-      </c>
-      <c r="G64" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I64" s="10"/>
@@ -14527,18 +14528,18 @@
         <v>0</v>
       </c>
       <c r="D65" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E65" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F65" s="9">
+        <v>55</v>
+      </c>
+      <c r="G65" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E65" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F65" s="9">
-        <v>55</v>
-      </c>
-      <c r="G65" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I65" s="10"/>
@@ -14554,18 +14555,18 @@
         <v>0</v>
       </c>
       <c r="D66" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E66" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F66" s="9">
+        <v>55</v>
+      </c>
+      <c r="G66" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E66" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F66" s="9">
-        <v>55</v>
-      </c>
-      <c r="G66" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I66" s="10"/>
@@ -14581,18 +14582,18 @@
         <v>0</v>
       </c>
       <c r="D67" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E67" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F67" s="9">
+        <v>55</v>
+      </c>
+      <c r="G67" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E67" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F67" s="9">
-        <v>55</v>
-      </c>
-      <c r="G67" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I67" s="10"/>
@@ -14608,18 +14609,18 @@
         <v>0</v>
       </c>
       <c r="D68" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E68" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F68" s="9">
+        <v>55</v>
+      </c>
+      <c r="G68" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E68" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F68" s="9">
-        <v>55</v>
-      </c>
-      <c r="G68" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I68" s="10"/>
@@ -14635,18 +14636,18 @@
         <v>0</v>
       </c>
       <c r="D69" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E69" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F69" s="9">
+        <v>55</v>
+      </c>
+      <c r="G69" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E69" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F69" s="9">
-        <v>55</v>
-      </c>
-      <c r="G69" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I69" s="10"/>
@@ -14662,18 +14663,18 @@
         <v>0</v>
       </c>
       <c r="D70" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E70" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F70" s="9">
+        <v>55</v>
+      </c>
+      <c r="G70" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E70" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F70" s="9">
-        <v>55</v>
-      </c>
-      <c r="G70" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I70" s="10"/>
@@ -14689,18 +14690,18 @@
         <v>0</v>
       </c>
       <c r="D71" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E71" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F71" s="9">
+        <v>55</v>
+      </c>
+      <c r="G71" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E71" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F71" s="9">
-        <v>55</v>
-      </c>
-      <c r="G71" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I71" s="10"/>
@@ -14716,18 +14717,18 @@
         <v>0</v>
       </c>
       <c r="D72" s="9">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="E72" s="9">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="F72" s="9">
+        <v>55</v>
+      </c>
+      <c r="G72" s="9">
         <f t="shared" si="14"/>
-        <v>3</v>
-      </c>
-      <c r="E72" s="9">
-        <f t="shared" si="15"/>
-        <v>6</v>
-      </c>
-      <c r="F72" s="9">
-        <v>55</v>
-      </c>
-      <c r="G72" s="9">
-        <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="I72" s="10"/>
@@ -16497,15 +16498,15 @@
       </c>
       <c r="B138" s="11"/>
       <c r="C138" s="8">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="D138" s="9">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>26.12</v>
       </c>
       <c r="E138" s="9">
         <f t="shared" si="21"/>
-        <v>6</v>
+        <v>52.24</v>
       </c>
       <c r="F138" s="9">
         <v>55</v>

--- a/CHARMS COLGANTES DISNEY.xlsx
+++ b/CHARMS COLGANTES DISNEY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BE15C8-283E-431F-B9EC-B36990C02E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91565274-C098-4947-B27B-301F33E95891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{44B837E0-01FB-47FB-9746-0A32C4320ACA}"/>
   </bookViews>
@@ -12992,7 +12992,9 @@
         <v>80</v>
       </c>
       <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
       <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -13020,9 +13022,7 @@
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="10"/>
-      <c r="K9" s="10">
-        <v>1</v>
-      </c>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
@@ -13405,7 +13405,9 @@
         <v>70</v>
       </c>
       <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="J23" s="10">
+        <v>1</v>
+      </c>
       <c r="K23" s="10"/>
     </row>
     <row r="24" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -13946,9 +13948,7 @@
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>
-      <c r="K43" s="10">
-        <v>1</v>
-      </c>
+      <c r="K43" s="10"/>
     </row>
     <row r="44" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
@@ -14165,7 +14165,9 @@
         <v>75</v>
       </c>
       <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
+      <c r="J51" s="10">
+        <v>1</v>
+      </c>
       <c r="K51" s="10"/>
     </row>
     <row r="52" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -14435,7 +14437,9 @@
         <v>70</v>
       </c>
       <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
+      <c r="J61" s="10">
+        <v>1</v>
+      </c>
       <c r="K61" s="10"/>
     </row>
     <row r="62" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
